--- a/horizon excursion/35 years - bundles as antigen (ONGOING)/Starting_point.xlsx
+++ b/horizon excursion/35 years - bundles as antigen (ONGOING)/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\Github\Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/35 years - bundles as antigen (ONGOING)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CFE0EDF-298A-4258-BD77-7F88B783553B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -18,17 +18,28 @@
     <sheet name="I_start" sheetId="4" r:id="rId3"/>
     <sheet name="S_start" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
   <si>
     <t>Measles</t>
   </si>
@@ -136,9 +147,6 @@
   </si>
   <si>
     <t>Xiamen_Innovax</t>
-  </si>
-  <si>
-    <t>Bharat_Biotech</t>
   </si>
   <si>
     <t>Pfizer</t>
@@ -153,7 +161,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="0.000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -225,7 +233,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -244,6 +252,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,11 +522,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
@@ -523,7 +535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -545,7 +557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -556,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -567,7 +579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -578,7 +590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -589,7 +601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -600,7 +612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -611,7 +623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -622,7 +634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -633,7 +645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -644,7 +656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -662,16 +674,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86710C76-81AC-48E5-8A5F-29B3CE6BD5DC}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.85546875" style="2"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="2"/>
+    <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -688,7 +700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -702,10 +714,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="4">
-        <v>13299464</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10639571.200000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -719,10 +731,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>12505034</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10004027.200000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -736,10 +748,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="3">
-        <v>13547121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10837696.800000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -753,10 +765,10 @@
         <v>3</v>
       </c>
       <c r="E5" s="4">
-        <v>6547121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5237696.8000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -770,10 +782,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="4">
-        <v>90279149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>72223319.200000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -787,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>180177056</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>144141644.80000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -804,10 +816,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>13305452</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10644361.600000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -821,10 +833,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>8948035</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7158428</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -838,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>140931564</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112745251.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -855,10 +867,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="4">
-        <v>17896071</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14316856.800000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -872,10 +884,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <v>31318125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25054500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -889,10 +901,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>53688215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>42950572</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -906,10 +918,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>43365104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>34692083.200000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -923,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="4">
-        <v>40213942</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>32171153.600000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -940,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="4">
-        <v>219201481</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>175361184.80000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -957,10 +969,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>61220888</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>48976710.400000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -974,10 +986,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="4">
-        <v>84680592</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>67744473.600000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -991,10 +1003,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="4">
-        <v>3625021</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2900016.8000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -1008,10 +1020,10 @@
         <v>5</v>
       </c>
       <c r="E20" s="4">
-        <v>13464366</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10771492.800000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1025,10 +1037,10 @@
         <v>5</v>
       </c>
       <c r="E21" s="4">
-        <v>5390769</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4312615.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -1042,29 +1054,29 @@
         <v>1</v>
       </c>
       <c r="E22" s="4">
-        <v>56510400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45208320</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>148530433.59999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
@@ -1073,18 +1085,18 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>16000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -1092,42 +1104,8 @@
       <c r="D25" s="2">
         <v>3</v>
       </c>
-      <c r="E25" s="4">
-        <v>185663042</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="2">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2">
-        <v>3</v>
-      </c>
-      <c r="E27" s="4">
-        <v>148533333</v>
+      <c r="E25" s="3">
+        <v>118826666.40000001</v>
       </c>
     </row>
   </sheetData>
@@ -1138,9 +1116,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBA2FAA-95C5-423D-A8C0-3A912D67D407}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1156,7 +1134,7 @@
         <v>12542</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1164,7 +1142,7 @@
         <v>7598</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1172,7 +1150,7 @@
         <v>14598</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1188,21 +1166,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C2B8D5-A351-43B6-AB72-03AAE787B34B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1188,7 @@
         <v>37210000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1218,7 +1196,7 @@
         <v>2610000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1226,7 +1204,7 @@
         <v>35730000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1212,7 @@
         <v>5706000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1220,7 @@
         <v>5777000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1250,7 +1228,7 @@
         <v>3207000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,7 +1236,7 @@
         <v>2595000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1266,7 +1244,7 @@
         <v>3123000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1252,7 @@
         <v>5222000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1282,7 +1260,7 @@
         <v>1900000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1290,7 +1268,7 @@
         <v>14250000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>

--- a/horizon excursion/35 years - bundles as antigen (ONGOING)/Starting_point.xlsx
+++ b/horizon excursion/35 years - bundles as antigen (ONGOING)/Starting_point.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/35 years - bundles as antigen (ONGOING)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CFE0EDF-298A-4258-BD77-7F88B783553B}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="114_{E2F6EBB1-4F5D-44B4-A2B9-4DC80064E476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86E1DA90-FD72-4118-9D8C-E450FF8E23A6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,28 +18,17 @@
     <sheet name="I_start" sheetId="4" r:id="rId3"/>
     <sheet name="S_start" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
   <si>
     <t>Measles</t>
   </si>
@@ -147,6 +136,9 @@
   </si>
   <si>
     <t>Xiamen_Innovax</t>
+  </si>
+  <si>
+    <t>Bharat_Biotech</t>
   </si>
   <si>
     <t>Pfizer</t>
@@ -252,10 +244,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -526,7 +514,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
@@ -674,7 +662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86710C76-81AC-48E5-8A5F-29B3CE6BD5DC}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="2"/>
@@ -714,7 +702,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4">
-        <v>10639571.200000001</v>
+        <v>13299464</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -731,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>10004027.200000001</v>
+        <v>12505034</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -748,7 +736,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="3">
-        <v>10837696.800000001</v>
+        <v>13547121</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -765,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="4">
-        <v>5237696.8000000007</v>
+        <v>6547121</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -782,7 +770,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="4">
-        <v>72223319.200000003</v>
+        <v>90279149</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -799,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>144141644.80000001</v>
+        <v>180177056</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -816,7 +804,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>10644361.600000001</v>
+        <v>13305452</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -833,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>7158428</v>
+        <v>8948035</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -850,7 +838,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>112745251.2</v>
+        <v>140931564</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -867,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="4">
-        <v>14316856.800000001</v>
+        <v>17896071</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -884,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <v>25054500</v>
+        <v>31318125</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -901,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>42950572</v>
+        <v>53688215</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -918,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>34692083.200000003</v>
+        <v>43365104</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -935,7 +923,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="4">
-        <v>32171153.600000001</v>
+        <v>40213942</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -952,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="4">
-        <v>175361184.80000001</v>
+        <v>219201481</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -969,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>48976710.400000006</v>
+        <v>61220888</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -986,7 +974,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="4">
-        <v>67744473.600000009</v>
+        <v>84680592</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1003,7 +991,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="4">
-        <v>2900016.8000000003</v>
+        <v>3625021</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1020,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="4">
-        <v>10771492.800000001</v>
+        <v>13464366</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1037,7 +1025,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="4">
-        <v>4312615.2</v>
+        <v>5390769</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1054,29 +1042,29 @@
         <v>1</v>
       </c>
       <c r="E22" s="4">
-        <v>45208320</v>
+        <v>56510400</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>148530433.59999999</v>
+        <v>565104</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
@@ -1085,10 +1073,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>16000000</v>
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>565104</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1096,7 +1084,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -1104,8 +1092,42 @@
       <c r="D25" s="2">
         <v>3</v>
       </c>
-      <c r="E25" s="3">
-        <v>118826666.40000001</v>
+      <c r="E25" s="4">
+        <v>185663042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
+        <v>148533333</v>
       </c>
     </row>
   </sheetData>
@@ -1168,13 +1190,13 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>18</v>
